--- a/光伏配储项目/电价数据/2026/柘林A厂.xlsx
+++ b/光伏配储项目/电价数据/2026/柘林A厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.32115</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.27767</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.28643</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.29646</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07465999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.71189</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.59051</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17755</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27066</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22296</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.6011</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.44096</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.53008</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.91872</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44214</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.47186</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.93363</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.58654</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.98429</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.18953</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.05165</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.04946</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.2031</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.22691</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45656</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7340099999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.8121499999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.7390399999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6663</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.42471</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40382</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.38301</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.5856699999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.6646299999999999</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.80486</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.58552</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.45919</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50651</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.58416</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.5560900000000001</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.62719</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.56559</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.7907999999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.51184</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.44335</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.43995</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.8666200000000001</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.7907999999999999</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.7907000000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.9544400000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.8192200000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.05861</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.7907999999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.83487</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.49998</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.50102</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.47198</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.49951</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3291</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.43302</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.41795</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.45506</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.37753</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.98273</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.42417</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.61895</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.70838</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.7907000000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.59282</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.61433</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.43031</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50032</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.7067899999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6888200000000001</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.54876</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.77746</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.55165</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.41757</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.47989</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.4601</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7907000000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.7907000000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5922999999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48718</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6356900000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.45709</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.49311</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.33558</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42268</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43202</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.45212</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.37596</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48597</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.47657</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.26766</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.49686</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.43964</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.48757</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.7826900000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.5941799999999999</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.45336</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.40639</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.54908</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.57916</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.61993</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.5955499999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.65552</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.65086</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.6301</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50232</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.54337</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.5095</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.49743</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.48365</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.42609</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.4451</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28747</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13325</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40197</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.46175</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25485</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.23161</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.09777</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.28393</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03205</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27484</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42227</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31698</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.47343</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23904</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24566</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.42561</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28718</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19172</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.22478</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25025</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.40983</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.22496</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24752</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21383</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19158</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17286</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24838</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26989</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.08875</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03484</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04789</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04924</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00408</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20145</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04438</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27086</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.18912</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00358</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05452000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05452000000000001</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14031</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31606</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.56383</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.16984</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22474</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.45498</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.40264</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.47254</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.5409400000000001</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.52067</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15669</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92031</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91412</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8630599999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29609</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88742</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18698</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87022</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65265</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33078</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03284</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57201</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2071</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62191</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5384</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45589</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43721</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44369</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.47461</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.61776</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6571900000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.00112</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.01383</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87898</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46433</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6461699999999999</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28452</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17681</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26144</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26103</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27402</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26036</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27394</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29196</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32353</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.82436</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.5001</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45567</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.48932</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.24026</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.5001</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.47125</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.4616</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.5001</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.5001</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.46455</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.5001</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.5001</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.5234800000000001</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.40485</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.5601900000000001</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.3101</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.7521</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.75042</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.48144</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5151399999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.23211</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.46705</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.44906</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46861</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.43545</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38437</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38328</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38655</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.44822</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32918</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.21075</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.22224</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18585</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.21761</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.1846</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.24392</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.23771</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.04726</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18432</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.27397</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.21625</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.19245</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.23135</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.24811</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29159</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.42173</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39129</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28393</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.2481</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28079</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.27066</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28627</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30288</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29178</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28501</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.08896</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6542899999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.49285</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49397</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.45169</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43029</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5575399999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27676</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.44952</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.47036</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.61341</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.48836</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43125</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.54043</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41826</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.4744</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.47158</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42034</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28368</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30006</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27945</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19588</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18652</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27668</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27244</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27638</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27209</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.18914</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.18675</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.14982</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23314</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28997</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26102</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.18675</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19289</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.19921</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.16305</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.1549</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.23677</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.2517</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.41908</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26438</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.43644</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.25946</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28459</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28546</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28673</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.25089</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.2789700000000001</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.24284</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23304</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32074</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.02277</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28235</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28474</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27222</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27921</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27287</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28361</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29335</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.5757000000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.50403</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29637</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28234</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.43856</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.48953</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6151599999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5826699999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.61758</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.77596</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48302</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.43598</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31338</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28519</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.27828</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.43135</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41959</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43595</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46785</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.54662</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43555</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.41178</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.47547</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.46448</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.39362</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7019099999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5634199999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6462</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.31939</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40944</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.26781</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29245</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.009820000000000001</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27383</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28234</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27442</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.49402</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.49477</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.51877</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.55983</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.49467</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.25835</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.27983</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.3261</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.22718</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.25016</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.27952</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.23166</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16299</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.009470000000000001</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.26354</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.01126</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.01168</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.16256</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.02313</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19608</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.01324</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.15288</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15767</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19296</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.15501</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.15767</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.16033</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.01418</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.01429</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.03993</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.17364</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.17903</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.14548</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28284</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.04553</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.17075</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.25719</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.43819</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00037</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.05802</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.06372</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.27384</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.21162</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.06384000000000001</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.24244</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.26886</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.21786</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.22117</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.27091</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.21121</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.23353</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3311</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22876</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27355</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.03672</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18373</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18055</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26759</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.02263</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20025</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22165</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21132</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.02359</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.0369</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.02264</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.02264</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.02294</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.02294</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.02276</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19299</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.03707</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.02294</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.02291</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.1712</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.03689</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.0369</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.02222</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.01978</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24338</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.01978</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00852</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-4e-05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.24583</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01199</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02674</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03881</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04402</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.02485</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04952</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02541</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.05667000000000001</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.02979</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.26031</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.02253</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27969</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26608</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29485</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.00544</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27322</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.16285</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.15808</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.16233</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.15979</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.15602</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.14512</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.01851</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.01738</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.01526</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41957</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.18612</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27352</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.22981</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85215</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8577100000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08181999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.02489</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25156</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.54104</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00191</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06725</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47096</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.5012099999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.74182</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.57586</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.41613</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.7603799999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7603799999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.75983</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30746</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.45321</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.25906</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.18472</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25606</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25184</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24395</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.21144</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.24913</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19719</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.16123</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.19288</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.15599</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.15826</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.17528</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.22725</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.25259</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.20946</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.22674</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.22141</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.25816</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29128</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29624</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5679</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46845</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47215</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.20462</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5144099999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5179600000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41912</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31589</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49022</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.50259</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.53584</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.45096</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5518999999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49494</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.41814</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5918300000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.56892</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32284</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28435</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.24861</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.49424</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19824</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.28767</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.50331</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.45868</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.46255</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.51315</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42103</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.43674</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.51722</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.40888</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32796</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.53152</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47803</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40663</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.47754</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.5205700000000001</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5080899999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.5605399999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.47357</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33938</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17913</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14642</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.20106</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14612</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04532</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.11938</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.23115</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.27208</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14547</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14617</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18793</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.23005</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.20611</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.2213</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.20434</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.4074700000000001</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.41381</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.5487799999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.45384</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.50544</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.43739</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.43403</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.4157</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.35577</v>
       </c>
     </row>
   </sheetData>
